--- a/317 Newell St/Results/Excels/Rent Estimates.xlsx
+++ b/317 Newell St/Results/Excels/Rent Estimates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rentometer" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Zillow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="rentometer_zillow_user_avg_est" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rentometer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zillow" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rentometer_zillow_user_avg_est" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="10">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1200</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="13">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="14">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -646,7 +646,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.rentometer.com/analysis/3-bed/317-newell-st-barberton-oh-44203/on3TP32HDUw/quickview</t>
+          <t>https://www.rentometer.com/analysis/3-bed/317-newell-st-barberton-oh-44203/ZbNrTJglPQs/quickview</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1953</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="19">
@@ -668,7 +668,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>on3TP32HDUw</t>
+          <t>ZbNrTJglPQs</t>
         </is>
       </c>
     </row>
@@ -680,13 +680,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[{'rel': 'request pro report', 'href': 'https://www.rentometer.com/api/v1/request_pro_report?api_key=fHSGZM7POi6V5ZPR0w4CXA&amp;token=on3TP32HDUw'}, {'rel': 'nearby comps', 'href': 'https://www.rentometer.com/api/v1/nearby_comps?api_key=fHSGZM7POi6V5ZPR0w4CXA&amp;token=on3TP32HDUw'}]</t>
+          <t>[{'rel': 'request pro report', 'href': 'https://www.rentometer.com/api/v1/request_pro_report?api_key=fHSGZM7POi6V5ZPR0w4CXA&amp;token=ZbNrTJglPQs'}, {'rel': 'nearby comps', 'href': 'https://www.rentometer.com/api/v1/nearby_comps?api_key=fHSGZM7POi6V5ZPR0w4CXA&amp;token=ZbNrTJglPQs'}]</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B17" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1431</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1557</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="6">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1324.75</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="9">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1413</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="10">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1361.5</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="11">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>1360.333333333333</v>
+        <v>1300.333333333333</v>
       </c>
     </row>
     <row r="2">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1357.666666666667</v>
+        <v>1297.333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1262.375</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="4">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1348</v>
+        <v>1290.5</v>
       </c>
     </row>
   </sheetData>
